--- a/jogos_2024-12-27.xlsx
+++ b/jogos_2024-12-27.xlsx
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>PSS Sleman</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.34</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="N5" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AC5" t="n">
-        <v>1.98</v>
+        <v>1.69</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
+          <t>['11', '35', '59', '65']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['36', '50', '56', '86']</t>
-        </is>
-      </c>
       <c r="AG5" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.75</v>
+        <v>1.58</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.3</v>
+        <v>1.69</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4</v>
+        <v>2.28</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45653.375</v>
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PSS Sleman</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>4</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.07</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>3.96</v>
       </c>
       <c r="N6" t="n">
-        <v>3.46</v>
+        <v>6.18</v>
       </c>
       <c r="O6" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="X6" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.69</v>
+        <v>1.98</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['11', '35', '59', '65']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36', '50', '56', '86']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.58</v>
+        <v>2.75</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.28</v>
+        <v>4</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45653.375</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1564,7 +1564,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.98</v>
+        <v>2.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>2.33</v>
       </c>
       <c r="N9" t="n">
-        <v>1.76</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>2.4</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['19']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['74']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45653.45833333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,109 +1675,109 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD10" t="n">
         <v>2</v>
       </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['72', '80', '90+6']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45653.45833333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.73</v>
+        <v>4.98</v>
       </c>
       <c r="M11" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>7.27</v>
+        <v>1.76</v>
       </c>
       <c r="O11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.92</v>
+        <v>1.46</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['72', '80', '90+6']</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45653.45833333334</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="M12" t="n">
-        <v>2.33</v>
+        <v>3.13</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>3.99</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.75</v>
+        <v>9.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="S12" t="n">
-        <v>2.18</v>
+        <v>2.43</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8</v>
+        <v>3.46</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.04</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.17</v>
+        <v>2.98</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.4</v>
+        <v>2.13</v>
       </c>
       <c r="AI12" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45653.45833333334</v>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,19 +2217,19 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
         <v>6</v>
@@ -2241,7 +2241,7 @@
         <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U14" t="n">
         <v>1.23</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['22', '64']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45653.5</v>
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,19 +2346,19 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
         <v>6</v>
@@ -2370,7 +2370,7 @@
         <v>2.2</v>
       </c>
       <c r="T15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U15" t="n">
         <v>1.23</v>
@@ -2404,25 +2404,25 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
+          <t>['22', '64']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45653.5</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
         <v>1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.48</v>
+        <v>7.55</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.91</v>
       </c>
       <c r="N19" t="n">
-        <v>2.62</v>
+        <v>1.38</v>
       </c>
       <c r="O19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T19" t="n">
         <v>3</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.25</v>
       </c>
-      <c r="X19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AC19" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['25', '63', '90+2']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>['24', '54', '87']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.45</v>
+        <v>1.99</v>
       </c>
       <c r="AH19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2.05</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45653.69791666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>7.55</v>
+        <v>2.48</v>
       </c>
       <c r="M21" t="n">
-        <v>3.91</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>1.38</v>
+        <v>2.62</v>
       </c>
       <c r="O21" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>3.14</v>
+        <v>3.95</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI21" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['25', '63', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['24', '54', '87']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45653.69791666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.07</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>12.57</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>10.01</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.5</v>
       </c>
-      <c r="P22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>12</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.22</v>
-      </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.73</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="X22" t="n">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.07</v>
+        <v>4.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="AC22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>5.5</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45653.71875</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,23 +3352,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>1</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>1.07</v>
       </c>
       <c r="M23" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="N23" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P23" t="n">
         <v>3.1</v>
       </c>
-      <c r="N23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.93</v>
-      </c>
       <c r="Q23" t="n">
-        <v>3.65</v>
+        <v>12</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.73</v>
       </c>
       <c r="V23" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>2.8</v>
+        <v>6.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.33</v>
+        <v>2.07</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.2</v>
+        <v>1.79</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>5.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.9</v>
+        <v>1.14</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45653.71875</v>
